--- a/LOGIC DOCS/PPC_Sequences_Interlocks_with_Modbus_Addresses.xlsx
+++ b/LOGIC DOCS/PPC_Sequences_Interlocks_with_Modbus_Addresses.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2cbea413949857c2/WORK/Tandarei/PPC/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2cbea413949857c2/WORK/PPC_ENERGY/LOGIC DOCS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{F3C41819-9100-4A9D-83B4-33A8DAA1A1B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E7759A9-D5DE-45AA-8CE6-90748C46785C}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{F3C41819-9100-4A9D-83B4-33A8DAA1A1B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28D22216-A335-49A2-B65B-EF63058257EA}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PPC_Sequences" sheetId="1" r:id="rId1"/>
@@ -3944,9 +3944,11 @@
   <cols>
     <col min="1" max="1" width="17.5546875" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="11.6640625" customWidth="1"/>
-    <col min="4" max="4" width="10.88671875" customWidth="1"/>
-    <col min="5" max="7" width="10" customWidth="1"/>
+    <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.88671875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="38.6640625" customWidth="1"/>
     <col min="9" max="9" width="20.6640625" customWidth="1"/>
     <col min="10" max="10" width="15.33203125" customWidth="1"/>
